--- a/AI Audit Log_PhungGiaBao.xlsx
+++ b/AI Audit Log_PhungGiaBao.xlsx
@@ -1,43 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KÌ 7\SWD392\nopbaitap\ai-audit-log-tuilavetne\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05795F0A-6AA6-4423-9062-3B79C89F384C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4542B6E9-4BF0-45FF-9D47-B4FCCE8D85A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 2" sheetId="1" r:id="rId1"/>
     <sheet name="Week 3" sheetId="2" r:id="rId2"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 4" sheetId="3" r:id="rId3"/>
+    <sheet name="Week 5" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -669,19 +660,143 @@
       </rPr>
       <t xml:space="preserve"> Khớp hoàn toàn với yêu cầu "inherit from it" của đề bài.</t>
     </r>
+  </si>
+  <si>
+    <t>Slot 9</t>
+  </si>
+  <si>
+    <t>Slot 7</t>
+  </si>
+  <si>
+    <t>"Làm thế nào để thể hiện các DTO (Data
+Transfer Object) trong Class Diagram cho User Management Feature?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích DTO nên được tách thành các lớp riêng biệt 
+(như CreateUserDTO, UpdateUserDTO) và thể hiện bằng mũi tên Dependency từ Controller/Service đến DTO.
+Quyết định: Tôi thêm các DTO vào diagram để làm rõ luồng dữ liệu truyền giữa client và backend, tránh việc dùng trực tiếp Entity cho Request/Response.</t>
+  </si>
+  <si>
+    <t>"Phân tích quan hệ giữa Order và OrderItem: nên dùng Composition (hình thoi đặc) hay Aggregation (hình thoi rỗng)?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân tích rằng OrderItem không thể tồn tại độc lập nếu
+thiếu Order, do đó quan hệ Composition là chính xác nhất về mặt nghiệp vụ.
+Quyết định: Tôi điều chỉnh lại nét vẽ trên UML thành Composition để phản ánh đúng logic xóa cascade (xóa Order thì xóa luôn OrderItem).</t>
+  </si>
+  <si>
+    <t>"Cách biểu diễn kiểu dữ liệu Enum (ví dụ:
+UserRole gồm ADMIN, USER) chuẩn xác nhất trong Class Diagram là gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn sử dụng stereotype &lt;&lt;enumeration&gt;&gt; cho 1
+block riêng và dùng nét đứt (dependency) hoặc association để nối vào User Entity.
+Quyết định: Tôi tạo một block Enum riêng trên PlantUML để làm rõ các phân quyền thay vì chỉ để kiểu String trong thuộc tính role.</t>
+  </si>
+  <si>
+    <t>"Khi nào nên dùng Interface và khi nào
+dùng Abstract Class trong thiết kế Service layer? Sinh ví dụ bằng PlantUML."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân biệt: Interface dùng để định nghĩa contract (hành vi), Abstract Class dùng khi có logic dùng chung. AI cung cấp code PlantUML minh họa.
+Quyết định: Tôi áp dụng Interface cho IUserService để tuân thủ Dependency Inversion và giúp việc mock data khi viết Unit Test dễ dàng hơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Đánh giá mức độ coupling giữa UserController và EmailService trong biểu đồ hiện tại. Đề xuất cách giảm coupling."
+</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI chỉ ra việc Controller gọi trực tiếp service bên ngoài làm tăng coupling, đề xuất sử dụng Interface hoặc cơ chế Event-Driven.
+Quyết định: Tôi cập nhật Class Diagram, bổ sung IEmailService để decouple, giúp kiến trúc linh hoạt hơn nếu sau này đổi provider gửi mail.</t>
+  </si>
+  <si>
+    <t>"Kiểm tra cách thể hiện quan hệ One-to-
+many và Many-to-Many giữa User và Role trong Class Diagram (áp dụng với TypeORM)."</t>
+  </si>
+  <si>
+    <t>Phản hồi: Ai giải thích cách đặt multiplicity (1 to 0..* hoặc * to *) và
+gợi ý việc có nên hiển thị bảng trung gian (JoinTable) trên biểu đồ hay không.
+Quyết định: Với mức logic nghiệp vụ, tôi ẩn bảng trung gian và dùng multiplicity *..*. Nhưng tôi ghi chú lại để xử lý khi cấu hình Entity trong code.</t>
+  </si>
+  <si>
+    <t>"Phân biệt Repository pattern và DAO 
+pattern trong Class Diagram. Kiến trúc hiện tại của dự án nên dùng cái nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích DAO thường map trực tiếp 1-1 với DB table, 
+trong khi Repository làm việc với Domain Entity (chứa logic nghiệp vụ).
+Quyết định: Tôi quyết định sử dụng tên gọi và cấu trúc của Repository để đồng nhất với các framework/ORM hiện đại đang sử dụng.</t>
+  </si>
+  <si>
+    <t>"Các lớp Custom Exception (như NotFoundException,UnauthorizedException) có cần thiết phải vẽ vào Class Diagram không?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI khuyên chỉ nên đưa vào nếu Exception đó mang logic
+nghiệp vụ cốt lõi, còn lại không nên vẽ để tránh làm biểu đồ bị rối (cluttered).
+Quyết định: Tôi lược bỏ các Exception cơ bản khỏi Class Diagram tổng thể để giữ biểu đồ clean, tập trung vào Entity và Service chính.</t>
+  </si>
+  <si>
+    <t>"Phân tích luồng gọi API từ Client (Frontend
+React) đến Backend ExpressJS (qua các lớp Controller -&gt; Service -&gt; Repository) cho chức năng Đăng ký tài khoản."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI mô tả thứ tự gọi hàm tuần tự giữa các lifeline
+(đường đời) nhấn mạnh việc Controller nhận request, Service xử lý nghiệp vụ và Repository thao tác với DB.
+Quyết định: Tôi dùng luồng này làm template chuẩn cho mọi API CRUD cơ bản trong báo cáo đồ án.</t>
+  </si>
+  <si>
+    <t>"Làm sao để thể hiện middleware (ví dụ: verifyToken dùng để check JWT) trong Sequence Diagram trước khi request thực sự đi vào Controller?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI gợi ý đặt middleware như 1 lifeline trung gian giữa
+Route/Router và Controller, sử dụng khối opt hoặc trả về lỗi 401 ngay lập tức nếu token không hợp lệ.
+Quyết định: Tôi bổ sung lifeline AuthMiddleware để làm rõ luồng bảo mật, sát với source code thực tế.</t>
+  </si>
+  <si>
+    <t>"Vẽ Sequence Diagram cho chức năng đăng
+nhập. Hướng dẫn cách sử dụng alt fragment để xử lý hai trường hợp phân nhánh: Sai mật khẩu và Đăng nhập thành công."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích cú pháp khung alt/else trong UML để bọc
+các luồng xử lý điều kiện if/else.
+Quyết định: Tôi áp dụng alt để tách bạch rõ ràng thông điệp trả về (Error message vs. Trả về Access Token).</t>
+  </si>
+  <si>
+    <t>"Thể hiện việc hệ thống gọi ra 1 external system (ví dụ: Gọi API của VNPay để thanh toán hoặc Nodemailer để gửi email OTP) trong Sequence Diagram như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI khuyên nên tạo 1 actor/lifeline nằm ngoài cùng
+bên phải với stereotype &lt;&lt;External System&gt;&gt; và dùng nét đứt để biểu diễn kết quả trả về chậm (callback).
+Quyết định: Tôi phân định rõ ranh giới hệ thống, giúp thấy rõ service nào đang phụ thuộc vào bên thứ ba.</t>
+  </si>
+  <si>
+    <t>"Sinh mã PlantUML cho sequence diagram
+chức năng Reset Password (Quên mật khẩu), bao gồm các lifeline: User, Client, AuthController, UserService, EmailService."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cung cấp code PlantUML với cấu trúc khai báo
+actor, boundary, control, entity và các mũi tên -&gt;, --&gt;.
+Quyết định: Tôi tái sử dụng và tinh chỉnh mã này để chèn thẳng vào tài liệu phân tích thiết kế, tiết kiệm thời gian vẽ tay.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -753,7 +868,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -762,23 +877,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -1238,100 +1353,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" s="10">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1342,18 +1457,282 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="27.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="54.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" customWidth="1"/>
+    <col min="4" max="4" width="50.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>